--- a/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
+++ b/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ansamcal.sharepoint.com/sites/CBGPackagingLineOperations/Shared Documents/General/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED3841B-C042-4E2E-BA0F-D396709C4721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B88A24E-AC18-4C82-B38B-4FA618077E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4254,7 +4254,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000012-112F-4FBE-BB51-673234708240}"/>
+                        <c16:uniqueId val="{00000012-246F-4461-8926-B489BF549057}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>

--- a/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
+++ b/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ansamcal.sharepoint.com/sites/CBGPackagingLineOperations/Shared Documents/General/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B88A24E-AC18-4C82-B38B-4FA618077E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB611B8A-73EB-462C-8D52-A167D6A0FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="10" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2026 (w Utilization)" sheetId="39" r:id="rId1"/>
@@ -984,7 +984,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="160">
   <si>
     <t>OEE Calculation</t>
   </si>
@@ -2928,16 +2928,16 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.7805673077781069</c:v>
+                  <c:v>0.7947444035555471</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86785347483774256</c:v>
+                  <c:v>0.86786296900537074</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.90152629233511583</c:v>
+                  <c:v>0.91778966131907314</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99766687799731879</c:v>
+                  <c:v>0.99777624354757888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3084,16 +3084,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.2194326922218931</c:v>
+                  <c:v>0.2052555964444529</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13214652516225744</c:v>
+                  <c:v>0.13213703099462926</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.8473707664884169E-2</c:v>
+                  <c:v>8.2210338680926864E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.3331220026812094E-3</c:v>
+                  <c:v>2.2237564524211217E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4254,7 +4254,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000012-246F-4461-8926-B489BF549057}"/>
+                        <c16:uniqueId val="{00000012-9018-4ADB-B2E7-A8C693DDDE96}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -22902,56 +22902,86 @@
       </c>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7" s="29"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6" t="str">
+      <c r="A7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46302.347222222219</v>
+      </c>
+      <c r="C7" s="5">
+        <v>46302.872916666667</v>
+      </c>
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8" t="str">
+        <v>757.0000000053551</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <f>5+7+7</f>
+        <v>19</v>
+      </c>
+      <c r="I7" s="7">
+        <f>2+2+2+3+1+4+3+4+3+2+3+2+3+1+1+2+2+2+2+2+3+2+4+4+2+1+1+1+3+2+3+2+2+1+2+2</f>
+        <v>81</v>
+      </c>
+      <c r="J7" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="9" t="str">
+        <v>0.86789960369974561</v>
+      </c>
+      <c r="K7" s="28">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28">
+        <f>4+4+3+3+3+2+4</f>
+        <v>23</v>
+      </c>
+      <c r="M7" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="9" t="str">
+        <v>0.83751651255068704</v>
+      </c>
+      <c r="N7" s="7">
+        <v>17000</v>
+      </c>
+      <c r="O7" s="15">
+        <f>AVERAGE(17000,17000,18000,18000,17000,17000,16500,17000,18000,15000,15000,15000)</f>
+        <v>16708.333333333332</v>
+      </c>
+      <c r="P7" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
+        <v>0.98284313725490191</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>6158</v>
+      </c>
+      <c r="R7" s="15">
+        <v>11</v>
+      </c>
       <c r="S7" s="7"/>
       <c r="T7" s="5"/>
       <c r="U7" s="10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="V7" s="9" t="str">
+      <c r="V7" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W7" s="11" t="str">
+        <v>0.99821370574861967</v>
+      </c>
+      <c r="W7" s="11">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X7" s="11" t="str">
+        <v>0.85148544394700854</v>
+      </c>
+      <c r="X7" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.82167697330679301</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -24552,7 +24582,7 @@
       <c r="C38" s="32"/>
       <c r="D38" s="33">
         <f>SUM(D3:D37)</f>
-        <v>2921.0000000079162</v>
+        <v>3678.0000000132713</v>
       </c>
       <c r="E38" s="33">
         <f>SUM(E3:E37)</f>
@@ -24568,15 +24598,15 @@
       </c>
       <c r="H38" s="33">
         <f>SUM(H2:H37)</f>
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="I38" s="33">
         <f>SUM(I3:I37)</f>
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="J38" s="34">
         <f>(D38-G38-H38-I38)/D38</f>
-        <v>0.86785347483774256</v>
+        <v>0.86786296900537074</v>
       </c>
       <c r="K38" s="35">
         <f>SUM(K3:K37)</f>
@@ -24584,11 +24614,11 @@
       </c>
       <c r="L38" s="35">
         <f>SUM(L3:L37)</f>
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="M38" s="36">
         <f>(D38-G38-H38-I38-E38-K38-L38)/D38</f>
-        <v>0.79219445395468846</v>
+        <v>0.80152256661300547</v>
       </c>
       <c r="N38" s="37">
         <f>AVERAGE(N3:N37)</f>
@@ -24596,15 +24626,15 @@
       </c>
       <c r="O38" s="38">
         <f>AVERAGE(O3:O37)</f>
-        <v>15325.94696969697</v>
+        <v>15602.424242424244</v>
       </c>
       <c r="P38" s="34">
         <f>O38/N38</f>
-        <v>0.90152629233511583</v>
+        <v>0.91778966131907314</v>
       </c>
       <c r="Q38" s="37">
         <f>SUM(Q3:Q35)</f>
-        <v>20139</v>
+        <v>26297</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="32"/>
@@ -24612,15 +24642,15 @@
       <c r="U38" s="39"/>
       <c r="V38" s="40">
         <f>AVERAGE(V3:V37)</f>
-        <v>0.99766687799731879</v>
+        <v>0.99777624354757888</v>
       </c>
       <c r="W38" s="41">
         <f>V38*P38*J38</f>
-        <v>0.7805673077781069</v>
+        <v>0.7947444035555471</v>
       </c>
       <c r="X38" s="42">
         <f>V38*P38*M38</f>
-        <v>0.71251785017715119</v>
+        <v>0.7339932649381451</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="28.5">
@@ -24643,7 +24673,7 @@
       <c r="S41" s="67"/>
       <c r="T41" s="46">
         <f>AVERAGE('January 2026 (w Utilization)'!X38,'February 2026 (w Utilization) '!X38,'March 2026 (w Utilization'!X38,'April 2026 (w Utilization) '!X38,'May 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'July 2026 (w Utilization)'!X38,'August 2026 (w Utilization)'!X38,'September 2026 (w Utilization)'!X38,'October 2026 (w Utilization) '!X38)</f>
-        <v>0.58137700462398412</v>
+        <v>0.58332931505680186</v>
       </c>
       <c r="U41" s="22"/>
     </row>
@@ -24683,11 +24713,11 @@
       </c>
       <c r="D47" s="16">
         <f>W38</f>
-        <v>0.7805673077781069</v>
+        <v>0.7947444035555471</v>
       </c>
       <c r="E47" s="18">
         <f>100%-D47</f>
-        <v>0.2194326922218931</v>
+        <v>0.2052555964444529</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -24696,11 +24726,11 @@
       </c>
       <c r="D48" s="16">
         <f>J38</f>
-        <v>0.86785347483774256</v>
+        <v>0.86786296900537074</v>
       </c>
       <c r="E48" s="18">
         <f>100%-D48</f>
-        <v>0.13214652516225744</v>
+        <v>0.13213703099462926</v>
       </c>
     </row>
     <row r="49" spans="3:5">
@@ -24709,11 +24739,11 @@
       </c>
       <c r="D49" s="16">
         <f>P38</f>
-        <v>0.90152629233511583</v>
+        <v>0.91778966131907314</v>
       </c>
       <c r="E49" s="18">
         <f>100%-D49</f>
-        <v>9.8473707664884169E-2</v>
+        <v>8.2210338680926864E-2</v>
       </c>
     </row>
     <row r="50" spans="3:5">
@@ -24723,11 +24753,11 @@
       </c>
       <c r="D50" s="16">
         <f>V38</f>
-        <v>0.99766687799731879</v>
+        <v>0.99777624354757888</v>
       </c>
       <c r="E50" s="18">
         <f>100%-D50</f>
-        <v>2.3331220026812094E-3</v>
+        <v>2.2237564524211217E-3</v>
       </c>
     </row>
   </sheetData>
@@ -24847,7 +24877,7 @@
       </c>
       <c r="L4" s="26">
         <f>'October 2026 (w Utilization) '!W38</f>
-        <v>0.7805673077781069</v>
+        <v>0.7947444035555471</v>
       </c>
       <c r="M4" s="26" t="e">
         <f>'November 2025 (w Utilization)'!W38</f>
@@ -24907,7 +24937,7 @@
       </c>
       <c r="L5" s="25">
         <f>AVERAGE($C$4:L4)</f>
-        <v>0.68624928173550059</v>
+        <v>0.6876669913132446</v>
       </c>
       <c r="M5" s="25" t="e">
         <f>AVERAGE($C$4:M4)</f>
@@ -51927,6 +51957,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010065A9D3CB8B02F24FBD87913D50150624" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="500ab49bf8b3ce09fa5e1a39689d4b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1dad3094-c8e6-4667-8455-c68e96f815a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9f2927e2397c07eda7eaadef1fb651c" ns2:_="">
     <xsd:import namespace="1dad3094-c8e6-4667-8455-c68e96f815a4"/>
@@ -52070,23 +52115,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D08D3D60-3D91-41A8-AAEA-3AD996B641F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0221E9-7351-4007-92F0-8B6A656CD9C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52094,5 +52124,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0221E9-7351-4007-92F0-8B6A656CD9C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D08D3D60-3D91-41A8-AAEA-3AD996B641F7}"/>
 </file>
--- a/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
+++ b/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ansamcal.sharepoint.com/sites/CBGPackagingLineOperations/Shared Documents/General/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB611B8A-73EB-462C-8D52-A167D6A0FFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C2D49DA-456B-4476-B16A-18ACEBF69628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="10" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="January 2026 (w Utilization)" sheetId="39" r:id="rId1"/>
@@ -984,7 +984,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="161">
   <si>
     <t>OEE Calculation</t>
   </si>
@@ -1466,6 +1466,9 @@
   </si>
   <si>
     <t>Starmalt to Vitamalt Classic</t>
+  </si>
+  <si>
+    <t>Carib Amber tp Stag</t>
   </si>
   <si>
     <t>January</t>
@@ -2928,13 +2931,13 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.7947444035555471</c:v>
+                  <c:v>0.79822557953444684</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86786296900537074</c:v>
+                  <c:v>0.86731919521526935</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.91778966131907314</c:v>
+                  <c:v>0.92238774297597825</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.99777624354757888</c:v>
@@ -3084,13 +3087,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.2052555964444529</c:v>
+                  <c:v>0.20177442046555316</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13213703099462926</c:v>
+                  <c:v>0.13268080478473065</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.2210338680926864E-2</c:v>
+                  <c:v>7.7612257024021747E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.2237564524211217E-3</c:v>
@@ -4254,7 +4257,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000012-9018-4ADB-B2E7-A8C693DDDE96}"/>
+                        <c16:uniqueId val="{00000012-0200-427D-93E2-DEFFF7C4DADB}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -22985,18 +22988,24 @@
       </c>
     </row>
     <row r="8" spans="1:24">
-      <c r="A8" s="29"/>
+      <c r="A8" s="29" t="s">
+        <v>145</v>
+      </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8" t="str">
+      <c r="E8" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="47"/>
@@ -23010,14 +23019,23 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="15"/>
+      <c r="N8" s="7">
+        <v>17000</v>
+      </c>
+      <c r="O8" s="15">
+        <f>AVERAGE(15000,15000,16000,15000,14000,16000,18000,18000,18000,18000,15500,15500,15500,15500)</f>
+        <v>16071.428571428571</v>
+      </c>
       <c r="P8" s="9" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
+      <c r="Q8" s="15">
+        <v>5473</v>
+      </c>
+      <c r="R8" s="15">
+        <v>24</v>
+      </c>
       <c r="S8" s="7"/>
       <c r="T8" s="5"/>
       <c r="U8" s="10" t="str">
@@ -24586,15 +24604,15 @@
       </c>
       <c r="E38" s="33">
         <f>SUM(E3:E37)</f>
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F38" s="33">
         <f>SUM(F3:F37)</f>
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G38" s="33">
         <f>SUM(G3:G37)</f>
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H38" s="33">
         <f>SUM(H2:H37)</f>
@@ -24606,7 +24624,7 @@
       </c>
       <c r="J38" s="34">
         <f>(D38-G38-H38-I38)/D38</f>
-        <v>0.86786296900537074</v>
+        <v>0.86731919521526935</v>
       </c>
       <c r="K38" s="35">
         <f>SUM(K3:K37)</f>
@@ -24618,7 +24636,7 @@
       </c>
       <c r="M38" s="36">
         <f>(D38-G38-H38-I38-E38-K38-L38)/D38</f>
-        <v>0.80152256661300547</v>
+        <v>0.7982599238723973</v>
       </c>
       <c r="N38" s="37">
         <f>AVERAGE(N3:N37)</f>
@@ -24626,15 +24644,15 @@
       </c>
       <c r="O38" s="38">
         <f>AVERAGE(O3:O37)</f>
-        <v>15602.424242424244</v>
+        <v>15680.591630591631</v>
       </c>
       <c r="P38" s="34">
         <f>O38/N38</f>
-        <v>0.91778966131907314</v>
+        <v>0.92238774297597825</v>
       </c>
       <c r="Q38" s="37">
         <f>SUM(Q3:Q35)</f>
-        <v>26297</v>
+        <v>31770</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="32"/>
@@ -24646,11 +24664,11 @@
       </c>
       <c r="W38" s="41">
         <f>V38*P38*J38</f>
-        <v>0.7947444035555471</v>
+        <v>0.79822557953444684</v>
       </c>
       <c r="X38" s="42">
         <f>V38*P38*M38</f>
-        <v>0.7339932649381451</v>
+        <v>0.73466780611723492</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="28.5">
@@ -24673,7 +24691,7 @@
       <c r="S41" s="67"/>
       <c r="T41" s="46">
         <f>AVERAGE('January 2026 (w Utilization)'!X38,'February 2026 (w Utilization) '!X38,'March 2026 (w Utilization'!X38,'April 2026 (w Utilization) '!X38,'May 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'July 2026 (w Utilization)'!X38,'August 2026 (w Utilization)'!X38,'September 2026 (w Utilization)'!X38,'October 2026 (w Utilization) '!X38)</f>
-        <v>0.58332931505680186</v>
+        <v>0.58339063698217364</v>
       </c>
       <c r="U41" s="22"/>
     </row>
@@ -24713,11 +24731,11 @@
       </c>
       <c r="D47" s="16">
         <f>W38</f>
-        <v>0.7947444035555471</v>
+        <v>0.79822557953444684</v>
       </c>
       <c r="E47" s="18">
         <f>100%-D47</f>
-        <v>0.2052555964444529</v>
+        <v>0.20177442046555316</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -24726,11 +24744,11 @@
       </c>
       <c r="D48" s="16">
         <f>J38</f>
-        <v>0.86786296900537074</v>
+        <v>0.86731919521526935</v>
       </c>
       <c r="E48" s="18">
         <f>100%-D48</f>
-        <v>0.13213703099462926</v>
+        <v>0.13268080478473065</v>
       </c>
     </row>
     <row r="49" spans="3:5">
@@ -24739,11 +24757,11 @@
       </c>
       <c r="D49" s="16">
         <f>P38</f>
-        <v>0.91778966131907314</v>
+        <v>0.92238774297597825</v>
       </c>
       <c r="E49" s="18">
         <f>100%-D49</f>
-        <v>8.2210338680926864E-2</v>
+        <v>7.7612257024021747E-2</v>
       </c>
     </row>
     <row r="50" spans="3:5">
@@ -24793,51 +24811,51 @@
         <v>24</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M3" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N3" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:18">
       <c r="B4" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C4" s="26">
         <f>'January 2026 (w Utilization)'!W38</f>
@@ -24877,7 +24895,7 @@
       </c>
       <c r="L4" s="26">
         <f>'October 2026 (w Utilization) '!W38</f>
-        <v>0.7947444035555471</v>
+        <v>0.79822557953444684</v>
       </c>
       <c r="M4" s="26" t="e">
         <f>'November 2025 (w Utilization)'!W38</f>
@@ -24897,7 +24915,7 @@
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C5" s="25">
         <f>C4</f>
@@ -24937,7 +24955,7 @@
       </c>
       <c r="L5" s="25">
         <f>AVERAGE($C$4:L4)</f>
-        <v>0.6876669913132446</v>
+        <v>0.6880151089111346</v>
       </c>
       <c r="M5" s="25" t="e">
         <f>AVERAGE($C$4:M4)</f>
@@ -24965,46 +24983,46 @@
     </row>
     <row r="32" spans="3:16" ht="18.75">
       <c r="C32" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M32" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P32" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="2:17" ht="30">
@@ -51957,18 +51975,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52116,11 +52134,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0221E9-7351-4007-92F0-8B6A656CD9C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77075DFF-DEDE-4E50-8ADC-F3E74E8E52C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77075DFF-DEDE-4E50-8ADC-F3E74E8E52C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0221E9-7351-4007-92F0-8B6A656CD9C4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
+++ b/data/raw/CBG OEE (Availability and Utilization) Calculation- 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ansamcal.sharepoint.com/sites/CBGPackagingLineOperations/Shared Documents/General/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C2D49DA-456B-4476-B16A-18ACEBF69628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5D7AE1E-FD71-404C-8810-2A81A2CAD36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="598" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -984,7 +984,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="162">
   <si>
     <t>OEE Calculation</t>
   </si>
@@ -1468,7 +1468,10 @@
     <t>Starmalt to Vitamalt Classic</t>
   </si>
   <si>
-    <t>Carib Amber tp Stag</t>
+    <t>Caribe Rose to Carib Flint (Local)</t>
+  </si>
+  <si>
+    <t>Carib Flint (Local) to Carib Amber</t>
   </si>
   <si>
     <t>January</t>
@@ -2931,16 +2934,16 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.79822557953444684</c:v>
+                  <c:v>0.74821229819867618</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86731919521526935</c:v>
+                  <c:v>0.8165879973027359</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.92238774297597825</c:v>
+                  <c:v>0.91864702109800156</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99777624354757888</c:v>
+                  <c:v>0.99740876211357432</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3087,16 +3090,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.20177442046555316</c:v>
+                  <c:v>0.25178770180132382</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13268080478473065</c:v>
+                  <c:v>0.1834120026972641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.7612257024021747E-2</c:v>
+                  <c:v>8.1352978901998441E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2237564524211217E-3</c:v>
+                  <c:v>2.5912378864256791E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4257,7 +4260,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000012-0200-427D-93E2-DEFFF7C4DADB}"/>
+                        <c16:uniqueId val="{00000012-B2D3-458C-A932-9BDEE0319B4C}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -22989,13 +22992,17 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6" t="str">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46303.333333333336</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46303.907638888886</v>
+      </c>
+      <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v/>
+        <v>826.99999999254942</v>
       </c>
       <c r="E8" s="7">
         <v>10</v>
@@ -23007,17 +23014,28 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="9" t="str">
+      <c r="H8" s="7">
+        <f>6+5+6+15+8+8+16+8+7+7+7+5</f>
+        <v>98</v>
+      </c>
+      <c r="I8" s="47">
+        <f>1+4+3+1+2+1+1+1+1+1+2+1+1+1+2+2+2+2+2+2+2+2+3+3+2+2+2+2+2+3+2+4</f>
+        <v>62</v>
+      </c>
+      <c r="J8" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="9" t="str">
+        <v>0.80411124546377333</v>
+      </c>
+      <c r="K8" s="28">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28">
+        <f>3+2+1+7+13+7+3+4</f>
+        <v>40</v>
+      </c>
+      <c r="M8" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.74365175332296263</v>
       </c>
       <c r="N8" s="7">
         <v>17000</v>
@@ -23026,9 +23044,9 @@
         <f>AVERAGE(15000,15000,16000,15000,14000,16000,18000,18000,18000,18000,15500,15500,15500,15500)</f>
         <v>16071.428571428571</v>
       </c>
-      <c r="P8" s="9" t="str">
+      <c r="P8" s="9">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0.94537815126050417</v>
       </c>
       <c r="Q8" s="15">
         <v>5473</v>
@@ -23042,176 +23060,266 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="V8" s="9" t="str">
+      <c r="V8" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W8" s="11" t="str">
+        <v>0.99561483646994331</v>
+      </c>
+      <c r="W8" s="11">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X8" s="11" t="str">
+        <v>0.75685564867694477</v>
+      </c>
+      <c r="X8" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.69994920892616097</v>
       </c>
     </row>
     <row r="9" spans="1:24">
-      <c r="A9" s="29"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6" t="str">
+      <c r="A9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46304.345833333333</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46304.791666666664</v>
+      </c>
+      <c r="D9" s="6">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8" t="str">
+        <v>641.99999999720603</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <f>16+6+5+6+23+14+6</f>
+        <v>76</v>
+      </c>
+      <c r="I9" s="7">
+        <f>1+1+2+2+3+2+1+5+3+2+1+4+2+2+1+3+2+1+2+2+2+2+1</f>
+        <v>47</v>
+      </c>
+      <c r="J9" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="9" t="str">
+        <v>0.80841121495243728</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28">
+        <f>2+2</f>
+        <v>4</v>
+      </c>
+      <c r="M9" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="9" t="str">
+        <v>0.80218068535739451</v>
+      </c>
+      <c r="N9" s="7">
+        <v>17000</v>
+      </c>
+      <c r="O9" s="15">
+        <f>AVERAGE(15000,16000,16000,16000,15500,15000,15000,15500,15000)</f>
+        <v>15444.444444444445</v>
+      </c>
+      <c r="P9" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
+        <v>0.90849673202614389</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>4674</v>
+      </c>
+      <c r="R9" s="15">
+        <v>9</v>
+      </c>
       <c r="S9" s="7"/>
       <c r="T9" s="5"/>
       <c r="U9" s="10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="V9" s="9" t="str">
+      <c r="V9" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W9" s="11" t="str">
+        <v>0.99807445442875486</v>
+      </c>
+      <c r="W9" s="11">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X9" s="11" t="str">
+        <v>0.73302475125598676</v>
+      </c>
+      <c r="X9" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.72737523486862687</v>
       </c>
     </row>
     <row r="10" spans="1:24">
-      <c r="A10" s="29"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6" t="str">
+      <c r="A10" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46307.388194444444</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46308</v>
+      </c>
+      <c r="D10" s="6">
         <f>IF(B10="","",(C10-B10)*24*60)</f>
-        <v/>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8" t="str">
+        <v>881.00000000093132</v>
+      </c>
+      <c r="E10" s="7">
+        <v>60</v>
+      </c>
+      <c r="F10" s="7">
+        <v>112</v>
+      </c>
+      <c r="G10" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="9" t="str">
+        <v>52</v>
+      </c>
+      <c r="H10" s="7">
+        <f>11+20+11+5+5+25+9+5+6+6+6+5+5</f>
+        <v>119</v>
+      </c>
+      <c r="I10" s="7">
+        <f>2+3+1+2+2+4+1+4</f>
+        <v>19</v>
+      </c>
+      <c r="J10" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="9" t="str">
+        <v>0.78433598183904751</v>
+      </c>
+      <c r="K10" s="28">
+        <v>0</v>
+      </c>
+      <c r="L10" s="28">
+        <f>2+40+13+7+20+60+5+23+9</f>
+        <v>179</v>
+      </c>
+      <c r="M10" s="9">
         <f>IF(B10="","",(D10-G10-H10-I10-K10-L10-E10)/D10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="7"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="9" t="str">
+        <v>0.51305334846816519</v>
+      </c>
+      <c r="N10" s="7">
+        <v>17000</v>
+      </c>
+      <c r="O10" s="15">
+        <f>AVERAGE(16000,15000,15000,15000,16000,17000,16000,17000)</f>
+        <v>15875</v>
+      </c>
+      <c r="P10" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
+        <v>0.93382352941176472</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>3593</v>
+      </c>
+      <c r="R10" s="15">
+        <v>17</v>
+      </c>
       <c r="S10" s="7"/>
       <c r="T10" s="5"/>
       <c r="U10" s="10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="V10" s="9" t="str">
+      <c r="V10" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W10" s="11" t="str">
+        <v>0.99526857779014755</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X10" s="11" t="str">
+        <v>0.72896595263700481</v>
+      </c>
+      <c r="X10" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.47683445816521131</v>
       </c>
     </row>
     <row r="11" spans="1:24">
-      <c r="A11" s="29"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6" t="str">
+      <c r="A11" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46308.036805555559</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46309</v>
+      </c>
+      <c r="D11" s="6">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8" t="str">
+        <v>1386.9999999948777</v>
+      </c>
+      <c r="E11" s="7">
+        <v>30</v>
+      </c>
+      <c r="F11" s="7">
+        <v>85</v>
+      </c>
+      <c r="G11" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="9" t="str">
+        <v>55</v>
+      </c>
+      <c r="H11" s="7">
+        <f>9+8+13+30+5+7+60+7+5+8+6+19+10+30+27+7</f>
+        <v>251</v>
+      </c>
+      <c r="I11" s="7">
+        <f>3+4+4+2+4+3+2+2+1+2+3+2+1+1+2+2+2+1+1+1+1+2+1+2+1+1+2+1+1+4+2+3+3+1+2+4+3+3+3+1+4+2+3</f>
+        <v>93</v>
+      </c>
+      <c r="J11" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="9" t="str">
+        <v>0.71232876712222526</v>
+      </c>
+      <c r="K11" s="28">
+        <v>0</v>
+      </c>
+      <c r="L11" s="28">
+        <f>12+24+18+3+1+1+4+5</f>
+        <v>68</v>
+      </c>
+      <c r="M11" s="9">
         <f>IF(B11="","",(D11-G11-H11-I11-K11-L11-E11)/D11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="7"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="9" t="str">
+        <v>0.64167267483645607</v>
+      </c>
+      <c r="N11" s="7">
+        <v>17000</v>
+      </c>
+      <c r="O11" s="15">
+        <f>AVERAGE(15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,15000,16000,16000,16000)</f>
+        <v>15150</v>
+      </c>
+      <c r="P11" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
+        <v>0.89117647058823535</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>8619</v>
+      </c>
+      <c r="R11" s="15">
+        <v>10</v>
+      </c>
       <c r="S11" s="7"/>
       <c r="T11" s="5"/>
       <c r="U11" s="10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="V11" s="9" t="str">
+      <c r="V11" s="9">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W11" s="11" t="str">
+        <v>0.99883977259542867</v>
+      </c>
+      <c r="W11" s="11">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X11" s="11" t="str">
+        <v>0.63407411188517737</v>
+      </c>
+      <c r="X11" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.57118012102984395</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -24600,31 +24708,31 @@
       <c r="C38" s="32"/>
       <c r="D38" s="33">
         <f>SUM(D3:D37)</f>
-        <v>3678.0000000132713</v>
+        <v>7414.9999999988358</v>
       </c>
       <c r="E38" s="33">
         <f>SUM(E3:E37)</f>
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="F38" s="33">
         <f>SUM(F3:F37)</f>
-        <v>114</v>
+        <v>311</v>
       </c>
       <c r="G38" s="33">
         <f>SUM(G3:G37)</f>
-        <v>-6</v>
+        <v>101</v>
       </c>
       <c r="H38" s="33">
         <f>SUM(H2:H37)</f>
-        <v>227</v>
+        <v>771</v>
       </c>
       <c r="I38" s="33">
         <f>SUM(I3:I37)</f>
-        <v>267</v>
+        <v>488</v>
       </c>
       <c r="J38" s="34">
         <f>(D38-G38-H38-I38)/D38</f>
-        <v>0.86731919521526935</v>
+        <v>0.8165879973027359</v>
       </c>
       <c r="K38" s="35">
         <f>SUM(K3:K37)</f>
@@ -24632,11 +24740,11 @@
       </c>
       <c r="L38" s="35">
         <f>SUM(L3:L37)</f>
-        <v>134</v>
+        <v>425</v>
       </c>
       <c r="M38" s="36">
         <f>(D38-G38-H38-I38-E38-K38-L38)/D38</f>
-        <v>0.7982599238723973</v>
+        <v>0.73095077545511622</v>
       </c>
       <c r="N38" s="37">
         <f>AVERAGE(N3:N37)</f>
@@ -24644,15 +24752,15 @@
       </c>
       <c r="O38" s="38">
         <f>AVERAGE(O3:O37)</f>
-        <v>15680.591630591631</v>
+        <v>15616.999358666026</v>
       </c>
       <c r="P38" s="34">
         <f>O38/N38</f>
-        <v>0.92238774297597825</v>
+        <v>0.91864702109800156</v>
       </c>
       <c r="Q38" s="37">
         <f>SUM(Q3:Q35)</f>
-        <v>31770</v>
+        <v>48656</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="32"/>
@@ -24660,15 +24768,15 @@
       <c r="U38" s="39"/>
       <c r="V38" s="40">
         <f>AVERAGE(V3:V37)</f>
-        <v>0.99777624354757888</v>
+        <v>0.99740876211357432</v>
       </c>
       <c r="W38" s="41">
         <f>V38*P38*J38</f>
-        <v>0.79822557953444684</v>
+        <v>0.74821229819867618</v>
       </c>
       <c r="X38" s="42">
         <f>V38*P38*M38</f>
-        <v>0.73466780611723492</v>
+        <v>0.66974577311919625</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="28.5">
@@ -24691,7 +24799,7 @@
       <c r="S41" s="67"/>
       <c r="T41" s="46">
         <f>AVERAGE('January 2026 (w Utilization)'!X38,'February 2026 (w Utilization) '!X38,'March 2026 (w Utilization'!X38,'April 2026 (w Utilization) '!X38,'May 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'June 2026 (w Utilization)'!X38,'July 2026 (w Utilization)'!X38,'August 2026 (w Utilization)'!X38,'September 2026 (w Utilization)'!X38,'October 2026 (w Utilization) '!X38)</f>
-        <v>0.58339063698217364</v>
+        <v>0.57748863398235184</v>
       </c>
       <c r="U41" s="22"/>
     </row>
@@ -24731,11 +24839,11 @@
       </c>
       <c r="D47" s="16">
         <f>W38</f>
-        <v>0.79822557953444684</v>
+        <v>0.74821229819867618</v>
       </c>
       <c r="E47" s="18">
         <f>100%-D47</f>
-        <v>0.20177442046555316</v>
+        <v>0.25178770180132382</v>
       </c>
     </row>
     <row r="48" spans="1:24">
@@ -24744,11 +24852,11 @@
       </c>
       <c r="D48" s="16">
         <f>J38</f>
-        <v>0.86731919521526935</v>
+        <v>0.8165879973027359</v>
       </c>
       <c r="E48" s="18">
         <f>100%-D48</f>
-        <v>0.13268080478473065</v>
+        <v>0.1834120026972641</v>
       </c>
     </row>
     <row r="49" spans="3:5">
@@ -24757,11 +24865,11 @@
       </c>
       <c r="D49" s="16">
         <f>P38</f>
-        <v>0.92238774297597825</v>
+        <v>0.91864702109800156</v>
       </c>
       <c r="E49" s="18">
         <f>100%-D49</f>
-        <v>7.7612257024021747E-2</v>
+        <v>8.1352978901998441E-2</v>
       </c>
     </row>
     <row r="50" spans="3:5">
@@ -24771,11 +24879,11 @@
       </c>
       <c r="D50" s="16">
         <f>V38</f>
-        <v>0.99777624354757888</v>
+        <v>0.99740876211357432</v>
       </c>
       <c r="E50" s="18">
         <f>100%-D50</f>
-        <v>2.2237564524211217E-3</v>
+        <v>2.5912378864256791E-3</v>
       </c>
     </row>
   </sheetData>
@@ -24811,51 +24919,51 @@
         <v>24</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M3" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N3" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="2:18">
       <c r="B4" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" s="26">
         <f>'January 2026 (w Utilization)'!W38</f>
@@ -24895,7 +25003,7 @@
       </c>
       <c r="L4" s="26">
         <f>'October 2026 (w Utilization) '!W38</f>
-        <v>0.79822557953444684</v>
+        <v>0.74821229819867618</v>
       </c>
       <c r="M4" s="26" t="e">
         <f>'November 2025 (w Utilization)'!W38</f>
@@ -24915,7 +25023,7 @@
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="25">
         <f>C4</f>
@@ -24955,7 +25063,7 @@
       </c>
       <c r="L5" s="25">
         <f>AVERAGE($C$4:L4)</f>
-        <v>0.6880151089111346</v>
+        <v>0.68301378077755748</v>
       </c>
       <c r="M5" s="25" t="e">
         <f>AVERAGE($C$4:M4)</f>
@@ -24983,46 +25091,46 @@
     </row>
     <row r="32" spans="3:16" ht="18.75">
       <c r="C32" s="24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M32" s="24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P32" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="2:17" ht="30">
@@ -51975,21 +52083,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010065A9D3CB8B02F24FBD87913D50150624" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="500ab49bf8b3ce09fa5e1a39689d4b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1dad3094-c8e6-4667-8455-c68e96f815a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9f2927e2397c07eda7eaadef1fb651c" ns2:_="">
     <xsd:import namespace="1dad3094-c8e6-4667-8455-c68e96f815a4"/>
@@ -52133,8 +52226,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77075DFF-DEDE-4E50-8ADC-F3E74E8E52C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D08D3D60-3D91-41A8-AAEA-3AD996B641F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52142,5 +52250,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D08D3D60-3D91-41A8-AAEA-3AD996B641F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77075DFF-DEDE-4E50-8ADC-F3E74E8E52C5}"/>
 </file>